--- a/Datos_de_prueba/01_caso_limpio/PL-03_toma_inventario_fisico.xlsx
+++ b/Datos_de_prueba/01_caso_limpio/PL-03_toma_inventario_fisico.xlsx
@@ -761,7 +761,7 @@
     <t>COMPUTADOR DE ESCRITORIO CORE I5</t>
   </si>
   <si>
-    <t>EQUIPO DE COMUNICACION Y COMPUTACION</t>
+    <t>EQUIPO DE COMUNICACION Y COMPUTO</t>
   </si>
   <si>
     <t>LENOVO</t>
